--- a/daily_matches/job_matches_2026-03-02.xlsx
+++ b/daily_matches/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Senior Python Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nest Veterinary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python, SQL</t>
+          <t>RAG, Copilot, FastAPI, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,112 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DevOps Engineer (Linux)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Quantifind</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Data Scientist, Docker, Kubernetes, Apache Airflow, Jenkins, Git, Hadoop, PostgreSQL, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Senior AI Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Riley Power Group</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bay City, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, AWS SageMaker, GCP Vertex AI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6340185b711d35</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AI Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Riley Power Group</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bay City, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, Copilot, Hugging Face, AWS SageMaker, GCP Vertex AI, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1153ccb0914b06a8</t>
+          <t>https://www.indeed.com/viewjob?jk=efb041473ea5610e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-02.xlsx
+++ b/daily_matches/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Python Engineer</t>
+          <t>Senior Backend Engineer (Ingeniero Senior de Backend) - Latin America (Remote) New</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nest Veterinary</t>
+          <t>Clara</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,17 +486,52 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Gemini, Docker, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb041473ea5610e</t>
+          <t>https://www.indeed.com/viewjob?jk=949a5230a377eb4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Python, AWS, GenAI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f391b396013e8c8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-02.xlsx
+++ b/daily_matches/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ingeniero Senior de Backend) - Latin America (Remote) New</t>
+          <t>Senior AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Clara</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gemini, Docker, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,182 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949a5230a377eb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2286c194c49eb0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, AWS, GenAI</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Decentral Holding Corporation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23b2396d3808220b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfb79ff7f7724d74</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Process Mining Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Noblesoft Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f391b396013e8c8</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75123cb7abb44bbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rohirrim</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d27a84de3ff1f75</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-02.xlsx
+++ b/daily_matches/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2286c194c49eb0</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, FastAPI, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Java Full Stack Engineer - Professional</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decentral Holding Corporation</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b2396d3808220b</t>
+          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb79ff7f7724d74</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Process Mining Engineer</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Noblesoft Technologies Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,427 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75123cb7abb44bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rohirrim</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, AKS, CI/CD, GitHub Actions, Terraform, Git, Tableau, Python, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c8add64b9180c0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Solutions Architect - AI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Robots &amp; Pencils</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Glue, Redshift, CI/CD, Terraform, Redshift, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kafka Cluster Support Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d4ea9dc6fb0c600</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fustis LLC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Norwalk, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, S3, Glue, Data Lake, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c3bd906cd851479</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Apache Airflow, CI/CD, Kafka, Hadoop, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1534e35cf264fdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineering Architect</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Plante Moran</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Southfield, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, CI/CD, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b68871ac3a81296</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning EngineerNew</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac9ae67ba53cef11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer-6</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Generative AI, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d27a84de3ff1f75</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8edd75e1dbb0f0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Applied AI Data Scientist (CEO Office)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TheSoul Group</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91128a60c17a9a57</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kafka Real Time Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Git, Kafka, Hadoop, Tableau, Power BI, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e1bbe4eeb6fb9c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kafka Real Time Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Synapse, Kafka, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bf6df71fea46ed5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1914606a75d90ac4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-02.xlsx
+++ b/daily_matches/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Sr Gen AI Engineer - NY/NJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3492813f1c56ca</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, FastAPI, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Generative AI, RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Professional</t>
+          <t>Senior Data Platform SIEM Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, S3, Data Lake, Kinesis, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Databricks, PySpark</t>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Docker, Kubernetes, Jenkins, Git, Hadoop, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>AI Security Software Engineer Intern - Summer 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, AKS, CI/CD, GitHub Actions, Terraform, Git, Tableau, Python, R</t>
+          <t>Generative AI, RAG, LLaMA, PyTorch, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8add64b9180c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=68a2648fcd8ad090</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Patch My PC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Glue, Redshift, CI/CD, Terraform, Redshift, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1fad6158a853f5a5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Fullstack developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4ea9dc6fb0c600</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4d58b13b159e04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Machine Learning Engineer - ThousandEyes</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Prompt Engineering, S3, Glue, Data Lake, Python, R, Java, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c3bd906cd851479</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d85f0cfcfae5e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II, Gen AI, Music</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Apache Airflow, CI/CD, Kafka, Hadoop, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, BigQuery, Dataflow, BigQuery, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1534e35cf264fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=9cba9ed2348af89c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Solutions Engineering Architect</t>
+          <t>RLHF Specialist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Odixcity Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, CI/CD, Terraform, Git, R, Scala</t>
+          <t>Machine Learning Engineer, LLaMA, Mistral, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b68871ac3a81296</t>
+          <t>https://www.indeed.com/viewjob?jk=99e5a37fd71b5e7d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning EngineerNew</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Power BI, Python, R, Scala</t>
+          <t>Machine Learning Engineer, Docker, Kubernetes, CI/CD, Snowflake, R, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac9ae67ba53cef11</t>
+          <t>https://www.indeed.com/viewjob?jk=c53f21951354c46c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer-6</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Cassandra, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8edd75e1dbb0f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad27f7660d3fbd6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Applied AI Data Scientist (CEO Office)</t>
+          <t>Senior DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TheSoul Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Git, Python, SQL, R, Scala</t>
+          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,112 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91128a60c17a9a57</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Kafka Real Time Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Git, Kafka, Hadoop, Tableau, Power BI, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1bbe4eeb6fb9c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Kafka Real Time Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Synapse, Kafka, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf6df71fea46ed5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Kafka API Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1914606a75d90ac4</t>
+          <t>https://www.indeed.com/viewjob?jk=81a3569aa45c7f5e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-02.xlsx
+++ b/daily_matches/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Gen AI Engineer - NY/NJ</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3492813f1c56ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d62af133e60ea749</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB</t>
+          <t>Data Scientist, Generative AI, Gemini, Prompt Engineering, Azure ML, Data Lake, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Platform SIEM Engineer</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Kinesis, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Senior Cloud DevOps Engineer (Azure &amp; AWS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Kubernetes, Jenkins, Git, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>RAG, Glue, Data Lake, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=30ad4f76b32130ff</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Security Software Engineer Intern - Summer 2026</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, PyTorch, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dataflow, Kubernetes, Databricks, Dask, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a2648fcd8ad090</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Patch My PC</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fad6158a853f5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=48d779cadb2f27d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fullstack developer</t>
+          <t>Data Scientist, Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4d58b13b159e04</t>
+          <t>https://www.indeed.com/viewjob?jk=d07af44b0b463505</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - ThousandEyes</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Git, Python, R, Scala</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d85f0cfcfae5e</t>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II, Gen AI, Music</t>
+          <t>Forward Deployed Engineer - AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Nexla</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Dataflow, BigQuery, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Prompt Engineering, BigQuery, AKS, Snowflake, Databricks, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cba9ed2348af89c</t>
+          <t>https://www.indeed.com/viewjob?jk=80cf3daa39e235c2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RLHF Specialist</t>
+          <t>Engineer AI and Machine Learning</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Odixcity Consulting</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LLaMA, Mistral, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Python, R, Optimization</t>
+          <t>Data Scientist, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e5a37fd71b5e7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c833308ca6f25876</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Docker, Kubernetes, CI/CD, Snowflake, R, Scala, Optimization, Bayesian</t>
+          <t>RAG, FastAPI, GitHub Actions, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53f21951354c46c</t>
+          <t>https://www.indeed.com/viewjob?jk=4da8b908cbfece17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Agentic AI Benchmarking and Evaluation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Cassandra, NoSQL, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad27f7660d3fbd6</t>
+          <t>https://www.indeed.com/viewjob?jk=f0d23cc5f978b152</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Remote</t>
+          <t>Senior Engineer, Machine Learning (ML Apps)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,707 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a3569aa45c7f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=7deaf01605663570</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ascendion</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, Copilot, Prompt Engineering, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af3ec9fa2c084c04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DevOps and CI Infrastructure Software Engineer (Multiple Levels)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fec10f0f2cfd615</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Career Mentors</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, Terraform, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9516c3688b6cd521</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mochi Health</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc2a9ad78bc9472c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Azure Platform Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Orion Innovation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Iselin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6fd7a7cf8e94feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BARTI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, MySQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f272f92eaffacbe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr AI Researcher for Agentic AI Core System Architecture</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0ad9cacfe6352e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sr Engineer, Machine Learning Engineering (Heterogenous SW, Adreno GPU)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=591bb58ae4d6e69d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Pinecone, Kubernetes, CI/CD, Terraform, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a7e58e9429e742a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer, AI Software Tools (Multiple Levels)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1454d85f62010ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Agentic Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87baa635dd767b6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineer Senior</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db49d789f1b3f126</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineer Senior</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc84e4af66404b9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ead975bbbae56910</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d42727583373bbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Boxborough, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e506686a794ad1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7f1cea6fb53d2a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=585e9fd017856469</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5d31caa344993df</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36ad3d3d004beb23</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-02.xlsx
+++ b/daily_matches/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62af133e60ea749</t>
+          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Sr. Data Analyst - Monetization &amp; Experimentation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>RedCloud Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Gemini, Prompt Engineering, Azure ML, Data Lake, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, S3, Athena, Redshift, Data Lake, Kubernetes, CI/CD, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a94bd965f7a37ae</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>JetBlue</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Snowflake, Databricks</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=04f094f9307fe9e0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Senior Software Engineer, Integration Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>RAG, EC2, Athena, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=b248613383f89a61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer (Azure &amp; AWS)</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Glue, Data Lake, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Data Scientist, S3, Glue, Redshift, Snowflake, Redshift, Hadoop, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ad4f76b32130ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dataflow, Kubernetes, Databricks, Dask, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, MLflow, CI/CD, Git, Databricks, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=8ede49a365f8b803</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Software Engineer</t>
+          <t>API Security IAM Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, S3, EC2, Glue, Athena, Terraform, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d779cadb2f27d6</t>
+          <t>https://www.indeed.com/viewjob?jk=080dd790549ca45e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist, Senior</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07af44b0b463505</t>
+          <t>https://www.indeed.com/viewjob?jk=b92cd5b30b4ca5ab</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>S3, Glue, Data Lake, CI/CD, GitHub Actions, Git, PySpark, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexla</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, BigQuery, AKS, Snowflake, Databricks, BigQuery, Kafka, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80cf3daa39e235c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8a341c21a7b661</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer AI and Machine Learning</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Snowflake, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c833308ca6f25876</t>
+          <t>https://www.indeed.com/viewjob?jk=76db373b98fa5c67</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, GitHub Actions, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, MLflow, CI/CD, Databricks, PySpark, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da8b908cbfece17</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Agentic AI Benchmarking and Evaluation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Python, R, Optimization</t>
+          <t>Data Scientist, RAG, Cortex, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0d23cc5f978b152</t>
+          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer, Machine Learning (ML Apps)</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Java, Optimization</t>
+          <t>RAG, S3, EC2, CI/CD, Jenkins, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7deaf01605663570</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, Copilot, Prompt Engineering, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, Copilot, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af3ec9fa2c084c04</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps and CI Infrastructure Software Engineer (Multiple Levels)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, PyTorch, AWS SageMaker, FastAPI, Docker, Databricks, PySpark, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fec10f0f2cfd615</t>
+          <t>https://www.indeed.com/viewjob?jk=ac45a1c90dd78d13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Terraform, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9516c3688b6cd521</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0cfb13b95e5931</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Kafka Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mochi Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
+          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2a9ad78bc9472c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b3cbc9d346731be</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Platform Full Stack Engineer</t>
+          <t>Kafka Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Databricks, Python, R, Java</t>
+          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fd7a7cf8e94feb</t>
+          <t>https://www.indeed.com/viewjob?jk=18ab0fab3c101359</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BARTI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, MySQL, SQL, R, Scala</t>
+          <t>RAG, Kinesis, Docker, Kubernetes, Terraform, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f272f92eaffacbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr AI Researcher for Agentic AI Core System Architecture</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, PyTorch, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Python, SQL, R, Julia, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ad9cacfe6352e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d4516597778f72f9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Engineer, Machine Learning Engineering (Heterogenous SW, Adreno GPU)</t>
+          <t>Senior AI Research Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Slingshot Aerospace</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,437 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Optimization</t>
+          <t>RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591bb58ae4d6e69d</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Pinecone, Kubernetes, CI/CD, Terraform, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7e58e9429e742a</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Software Engineer, AI Software Tools (Multiple Levels)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1454d85f62010ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Agentic Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87baa635dd767b6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI Machine Learning Engineer Senior</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Lockheed Martin</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db49d789f1b3f126</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Machine Learning Engineer Senior</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Lockheed Martin</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc84e4af66404b9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ead975bbbae56910</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d42727583373bbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Boxborough, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e506686a794ad1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f1cea6fb53d2a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=585e9fd017856469</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5d31caa344993df</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Artificial Intelligence Engineering Internship – Summer 2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=36ad3d3d004beb23</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a2acf7dd263d51</t>
         </is>
       </c>
     </row>
